--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486764_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486764_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2847</v>
+        <v>5.2377</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3974</v>
+        <v>4.1765</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8873</v>
+        <v>1.0612</v>
       </c>
       <c r="G2" t="n">
         <v>3.5757</v>
@@ -610,13 +610,13 @@
         <v>1.7377</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3256</v>
+        <v>0.6274</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6898</v>
+        <v>0.0893</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3643</v>
+        <v>0.5381</v>
       </c>
       <c r="V2" t="n">
         <v>1.2277</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BALDERAS MARTÍN</t>
+          <t>A. ANDRADE ROSSI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8488</v>
+        <v>2.4529</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6788</v>
+        <v>2.0402</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.83</v>
+        <v>0.4127</v>
       </c>
       <c r="G3" t="n">
-        <v>1.856</v>
+        <v>1.4396</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1447</v>
+        <v>2.1381</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7114</v>
+        <v>-0.6985</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4985</v>
+        <v>2.7234</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6628</v>
+        <v>2.7595</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8357</v>
+        <v>-0.0361</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6425</v>
+        <v>-1.2838</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5181</v>
+        <v>-0.6214</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1244</v>
+        <v>-0.6624</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5446</v>
+        <v>1.3515</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5446</v>
+        <v>2.3169</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1045</v>
+        <v>0.8895</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5511</v>
+        <v>0.2823</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4466</v>
+        <v>0.6072</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6565</v>
+        <v>-1.2277</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. MURRAY</t>
+          <t>J. BALDERAS MARTÍN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4408</v>
+        <v>2.4338</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1246</v>
+        <v>3.0652</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3162</v>
+        <v>-0.6314</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.5138</v>
+        <v>1.856</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3518</v>
+        <v>0.1447</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.162</v>
+        <v>1.7114</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.0092</v>
+        <v>3.4985</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1663</v>
+        <v>1.6628</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1755</v>
+        <v>1.8357</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5046</v>
+        <v>-1.6425</v>
       </c>
       <c r="N4" t="n">
         <v>-1.5181</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0135</v>
+        <v>-0.1244</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3515</v>
+        <v>1.5446</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3169</v>
+        <v>1.5446</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1476</v>
+        <v>-0.3104</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.028</v>
+        <v>-0.0625</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1756</v>
+        <v>-0.2479</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4554</v>
+        <v>-0.6565</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1271</v>
+        <v>-0.3709</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3282</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ANDRADE ROSSI</t>
+          <t>C. MURRAY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4296</v>
+        <v>2.3965</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6196</v>
+        <v>0.5521</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.8444</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4396</v>
+        <v>-2.5138</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1381</v>
+        <v>-1.3518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6985</v>
+        <v>-1.162</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7234</v>
+        <v>-1.0092</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7595</v>
+        <v>0.1663</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0361</v>
+        <v>-1.1755</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2838</v>
+        <v>-1.5046</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6214</v>
+        <v>-1.5181</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6624</v>
+        <v>0.0135</v>
       </c>
       <c r="P5" t="n">
         <v>1.3515</v>
@@ -844,28 +844,28 @@
         <v>2.3169</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8662</v>
+        <v>1.1034</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1384</v>
+        <v>0.3996</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0046</v>
+        <v>0.7038</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2277</v>
+        <v>2.4554</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.1271</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2277</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>M. MIJE BENITEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0112</v>
+        <v>0.4103</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6745</v>
+        <v>-0.2344</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3367</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.8143</v>
+        <v>-2.7519</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2137</v>
+        <v>-1.4339</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6005</v>
+        <v>-1.318</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6407</v>
+        <v>-1.2547</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1663</v>
+        <v>-0.6059</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.6488</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1736</v>
+        <v>-1.4972</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3801</v>
+        <v>-0.828</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7935</v>
+        <v>-0.6692</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5446</v>
+        <v>1.9308</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.51</v>
+        <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7096</v>
+        <v>0.9032</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7093</v>
+        <v>0.4065</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0002</v>
+        <v>0.4967</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5712</v>
+        <v>0.3282</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5712</v>
+        <v>0.6138</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MIJE BENITEZ</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3455</v>
+        <v>0.2322</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4482</v>
+        <v>-0.3528</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7937</v>
+        <v>0.585</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.7519</v>
+        <v>-2.8143</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4339</v>
+        <v>-1.2137</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.318</v>
+        <v>-1.6005</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2547</v>
+        <v>-0.6407</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6059</v>
+        <v>0.1663</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6488</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4972</v>
+        <v>-2.1736</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.828</v>
+        <v>-1.3801</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6692</v>
+        <v>-0.7935</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9308</v>
+        <v>1.5446</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9308</v>
+        <v>2.51</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8384</v>
+        <v>0.9306</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1927</v>
+        <v>0.6821</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.2486</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3282</v>
+        <v>0.5712</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6138</v>
+        <v>0.5712</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6962</v>
+        <v>-0.1307</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3239</v>
+        <v>0.6411</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0202</v>
+        <v>-0.7719</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0974</v>
@@ -1234,13 +1234,13 @@
         <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.993</v>
+        <v>-0.4275</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4691</v>
+        <v>-0.1519</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5239</v>
+        <v>-0.2756</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5712</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. VILLALBA BAULBYS</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6121</v>
+        <v>-1.0439</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2814</v>
+        <v>0.3116</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3307</v>
+        <v>-1.3555</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3444</v>
+        <v>-2.8714</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7994</v>
+        <v>-0.6832</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1439</v>
+        <v>-2.1882</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8153</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1106</v>
+        <v>1.1107</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2953</v>
+        <v>-2.0639</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1598</v>
+        <v>-1.9183</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3112</v>
+        <v>-1.7939</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1514</v>
+        <v>-0.1244</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5792</v>
+        <v>1.7377</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3515</v>
+        <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4028</v>
+        <v>-0.5241</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1659</v>
+        <v>-0.2486</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2369</v>
+        <v>-0.2755</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2856</v>
+        <v>0.6138</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2856</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>M. VILLALBA BAULBYS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6728</v>
+        <v>-1.5058</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2677</v>
+        <v>-1.2744</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4052</v>
+        <v>-0.2314</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8714</v>
+        <v>-0.3444</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6832</v>
+        <v>0.7994</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1882</v>
+        <v>-1.1439</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9530999999999999</v>
+        <v>0.8153</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1107</v>
+        <v>2.1106</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0639</v>
+        <v>-1.2953</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9183</v>
+        <v>-1.1598</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.7939</v>
+        <v>-1.3112</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1244</v>
+        <v>0.1514</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7377</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7377</v>
+        <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.153</v>
+        <v>-0.2965</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8279</v>
+        <v>-0.159</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3252</v>
+        <v>-0.1375</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6138</v>
+        <v>-0.2856</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8995</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.4209</v>
+        <v>10.5244</v>
       </c>
       <c r="E13" t="n">
-        <v>7.8629</v>
+        <v>8.9665</v>
       </c>
       <c r="F13" t="n">
         <v>1.5578</v>
@@ -1441,7 +1441,7 @@
         <v>-7.584199999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>8.804200000000002</v>
+        <v>8.8042</v>
       </c>
       <c r="K13" t="n">
         <v>13.7997</v>
@@ -1468,13 +1468,13 @@
         <v>16.4115</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7919</v>
+        <v>2.8956</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1340000000000002</v>
+        <v>1.2378</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6578</v>
+        <v>1.6579</v>
       </c>
       <c r="V13" t="n">
         <v>2.4553</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. GONZALEZ GRANDE</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.8814</v>
+        <v>6.1069</v>
       </c>
       <c r="E14" t="n">
-        <v>7.7587</v>
+        <v>7.2049</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8772</v>
+        <v>-1.098</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2101</v>
+        <v>6.9655</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7377</v>
+        <v>2.0893</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4724</v>
+        <v>4.8762</v>
       </c>
       <c r="J14" t="n">
-        <v>6.4532</v>
+        <v>8.732799999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>6.2904</v>
+        <v>4.2973</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1628</v>
+        <v>4.4354</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.2431</v>
+        <v>-1.7673</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.5527</v>
+        <v>-2.2081</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3096</v>
+        <v>0.4408</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7723</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1931</v>
+        <v>-3.0892</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1846</v>
+        <v>-0.4411</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2129</v>
+        <v>-0.5658</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9717</v>
+        <v>0.1247</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2856</v>
+        <v>1.5133</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2856</v>
+        <v>2.1271</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5712</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>R. GONZALEZ GRANDE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.5994</v>
+        <v>5.676</v>
       </c>
       <c r="E15" t="n">
-        <v>6.998</v>
+        <v>6.7244</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3986</v>
+        <v>-1.0484</v>
       </c>
       <c r="G15" t="n">
-        <v>6.9655</v>
+        <v>4.2101</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0893</v>
+        <v>3.7377</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8762</v>
+        <v>0.4724</v>
       </c>
       <c r="J15" t="n">
-        <v>8.732799999999999</v>
+        <v>6.4532</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2973</v>
+        <v>6.2904</v>
       </c>
       <c r="L15" t="n">
-        <v>4.4354</v>
+        <v>0.1628</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7673</v>
+        <v>-2.2431</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.2081</v>
+        <v>-2.5527</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4408</v>
+        <v>0.3096</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.9308</v>
+        <v>0.7723</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.0892</v>
+        <v>-0.1931</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9486</v>
+        <v>0.9792</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.1787</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1759</v>
+        <v>0.8005</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5133</v>
+        <v>-0.2856</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1271</v>
+        <v>0.2856</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6138</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8714</v>
+        <v>0.4218</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5537</v>
+        <v>1.14</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6823</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>2.4158</v>
@@ -1702,13 +1702,13 @@
         <v>0.7723</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4636</v>
+        <v>0.014</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2204</v>
+        <v>-0.1933</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2432</v>
+        <v>0.2073</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6565</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0999</v>
+        <v>-0.7938</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1452</v>
+        <v>-0.9384</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0453</v>
+        <v>0.1446</v>
       </c>
       <c r="G17" t="n">
         <v>0.5716</v>
@@ -1780,13 +1780,13 @@
         <v>0.1931</v>
       </c>
       <c r="S17" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.3724</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0827</v>
+        <v>0.2896</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0165</v>
+        <v>0.0828</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3262</v>
+        <v>-1.736</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2466</v>
+        <v>-0.8329</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0796</v>
+        <v>-0.9031</v>
       </c>
       <c r="G18" t="n">
         <v>-1.133</v>
@@ -1858,13 +1858,13 @@
         <v>0.3862</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.066</v>
+        <v>0.5242</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5243</v>
+        <v>-0.1106</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4583</v>
+        <v>0.6348</v>
       </c>
       <c r="V18" t="n">
         <v>-1.5133</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BRASSEUR</t>
+          <t>P. GRIMA LORENZO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.606</v>
+        <v>-2.6576</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6629</v>
+        <v>-1.9186</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9431</v>
+        <v>-0.739</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7126</v>
+        <v>0.1532</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0555</v>
+        <v>-1.5581</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3428</v>
+        <v>1.7113</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9231</v>
+        <v>0.9683</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2616</v>
+        <v>0.2358</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1846</v>
+        <v>0.7325</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6357</v>
+        <v>-0.8151</v>
       </c>
       <c r="N19" t="n">
         <v>-1.7939</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1582</v>
+        <v>0.9788</v>
       </c>
       <c r="P19" t="n">
+        <v>-1.3515</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-2.1239</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-3.0892</v>
-      </c>
       <c r="R19" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0978</v>
+        <v>-0.5172</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4968</v>
+        <v>-0.4348</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.601</v>
+        <v>-0.0824</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3282</v>
+        <v>-0.9421</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3282</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. GRIMA LORENZO</t>
+          <t>A. BRASSEUR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6299</v>
+        <v>-3.1909</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2288</v>
+        <v>-2.5595</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.401</v>
+        <v>-0.6314</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1532</v>
+        <v>-0.7126</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5581</v>
+        <v>-2.0555</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7113</v>
+        <v>1.3428</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9683</v>
+        <v>0.9231</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2358</v>
+        <v>-0.2616</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7325</v>
+        <v>1.1846</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8151</v>
+        <v>-1.6357</v>
       </c>
       <c r="N20" t="n">
         <v>-1.7939</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9788</v>
+        <v>0.1582</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3515</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1239</v>
+        <v>-3.0892</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4894</v>
+        <v>-0.6826</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.745</v>
+        <v>-0.3933</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7444</v>
+        <v>-0.2893</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9421</v>
+        <v>0.3282</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6138</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8389</v>
+        <v>-3.37</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5182</v>
+        <v>-2.3114</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3207</v>
+        <v>-1.0586</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4224</v>
@@ -2092,13 +2092,13 @@
         <v>0.3862</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5516</v>
+        <v>-0.0827</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3587</v>
+        <v>-0.1519</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1929</v>
+        <v>0.0692</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1188</v>
+        <v>-3.4968</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5001</v>
+        <v>-3.1898</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6187</v>
+        <v>-0.307</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9658</v>
@@ -2170,13 +2170,13 @@
         <v>0.3862</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5737</v>
+        <v>0.0483</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5243</v>
+        <v>-0.214</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0494</v>
+        <v>0.2623</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1533</v>
+        <v>-4.3119</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5662</v>
+        <v>-4.8765</v>
       </c>
       <c r="F23" t="n">
-        <v>0.413</v>
+        <v>0.5646</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6017</v>
@@ -2248,13 +2248,13 @@
         <v>0.7723</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2208</v>
+        <v>0.0622</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2479</v>
+        <v>-0.0624</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0271</v>
+        <v>0.1245</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6138</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.4208</v>
+        <v>-7.352299999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.557599999999999</v>
+        <v>-1.557799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.862900000000002</v>
+        <v>-5.794499999999999</v>
       </c>
       <c r="G24" t="n">
         <v>4.4807</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.103899999999999</v>
+        <v>-3.1039</v>
       </c>
       <c r="I24" t="n">
         <v>7.584300000000001</v>
@@ -2314,7 +2314,7 @@
         <v>-13.7998</v>
       </c>
       <c r="O24" t="n">
-        <v>4.9955</v>
+        <v>4.995500000000001</v>
       </c>
       <c r="P24" t="n">
         <v>-9.6538</v>
@@ -2326,13 +2326,13 @@
         <v>6.757899999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7919</v>
+        <v>0.2767000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.6579</v>
+        <v>-1.6578</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1339999999999999</v>
+        <v>1.9344</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4554</v>
